--- a/Data/data_TextMining/df_Cemex_reference.xlsx
+++ b/Data/data_TextMining/df_Cemex_reference.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,50 +387,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>yr</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>n_statement</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>goal_desc</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ind</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ind_agg</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ind_7sys</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ind_3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Continent</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
@@ -454,12 +459,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1_4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -468,41 +473,39 @@
         </is>
       </c>
       <c r="G2">
-        <v>23</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>2018</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>No Poverty</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Energy, natural resources, and basic materials</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -512,7 +515,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -534,12 +542,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1_g</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,41 +556,39 @@
         </is>
       </c>
       <c r="G3">
-        <v>6</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>2018</v>
+      </c>
+      <c r="H3">
+        <v>23</v>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>No Poverty</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Energy, natural resources, and basic materials</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -592,7 +598,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[5,7)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -609,60 +620,58 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10_2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SDG2</t>
+          <t>SDG10</t>
         </is>
       </c>
       <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Zero Hunger</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -672,7 +681,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -689,12 +703,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>10_3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -704,45 +718,43 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SDG2</t>
+          <t>SDG10</t>
         </is>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Zero Hunger</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -752,7 +764,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>[7,11)</t>
         </is>
       </c>
     </row>
@@ -769,60 +786,58 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>10_4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SDG2</t>
+          <t>SDG10</t>
         </is>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Zero Hunger</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -832,7 +847,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>[2,3)</t>
         </is>
       </c>
     </row>
@@ -849,60 +869,58 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>10_7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SDG2</t>
+          <t>SDG10</t>
         </is>
       </c>
       <c r="G7">
+        <v>2018</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Zero Hunger</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -911,6 +929,11 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>[1,2)</t>
         </is>
@@ -929,60 +952,58 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>10_b</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SDG3</t>
+          <t>SDG10</t>
         </is>
       </c>
       <c r="G8">
-        <v>131</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Good Health And Well-Being</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -992,7 +1013,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -1009,60 +1035,58 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>11_1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SDG3</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G9">
-        <v>400</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Good Health And Well-Being</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H9">
+        <v>125</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1072,7 +1096,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1118,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>11_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1104,45 +1133,43 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SDG3</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Good Health And Well-Being</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1152,7 +1179,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>[3,4)</t>
         </is>
       </c>
     </row>
@@ -1169,60 +1201,58 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.a</t>
+          <t>11_2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SDG3</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Good Health And Well-Being</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1232,7 +1262,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -1249,60 +1284,58 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>11_5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SDG3</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Good Health And Well-Being</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H12">
+        <v>16</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1312,7 +1345,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>[2,3)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -1329,60 +1367,58 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.a</t>
+          <t>11_7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G13">
-        <v>11</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1392,7 +1428,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>[3,4)</t>
         </is>
       </c>
     </row>
@@ -1409,60 +1450,58 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>11_b</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G14">
-        <v>137</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1472,7 +1511,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>[3,4)</t>
         </is>
       </c>
     </row>
@@ -1489,60 +1533,58 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>11_b</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G15">
-        <v>11</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1552,7 +1594,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>[3,4)</t>
         </is>
       </c>
     </row>
@@ -1569,60 +1616,58 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>11_g</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG11</t>
         </is>
       </c>
       <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H16">
+        <v>844</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Sustainable Cities And Communities</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1632,7 +1677,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1649,60 +1699,58 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>12_1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG12</t>
         </is>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H17">
+        <v>56</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Responsible Consumption And Production</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1712,7 +1760,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>[2,3)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1729,60 +1782,58 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.b</t>
+          <t>12_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SDG4</t>
+          <t>SDG12</t>
         </is>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Quality Education</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H18">
+        <v>88</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Responsible Consumption And Production</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1792,7 +1843,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1809,60 +1865,58 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5.a</t>
+          <t>12_4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SDG5</t>
+          <t>SDG12</t>
         </is>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Gender Equality</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H19">
+        <v>205</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Responsible Consumption And Production</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1872,7 +1926,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1889,60 +1948,58 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>12_5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5.b</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SDG5</t>
+          <t>SDG12</t>
         </is>
       </c>
       <c r="G20">
-        <v>16</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Gender Equality</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H20">
+        <v>37</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Responsible Consumption And Production</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1952,7 +2009,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -1969,60 +2031,58 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5.a</t>
+          <t>12_g</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SDG5</t>
+          <t>SDG12</t>
         </is>
       </c>
       <c r="G21">
-        <v>44</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Gender Equality</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H21">
+        <v>38</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Responsible Consumption And Production</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2032,7 +2092,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2049,60 +2114,58 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>13_2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SDG5</t>
+          <t>SDG13</t>
         </is>
       </c>
       <c r="G22">
-        <v>13</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Gender Equality</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H22">
+        <v>484</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Climate Action</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2112,7 +2175,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2129,60 +2197,58 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>13_2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SDG6</t>
+          <t>SDG13</t>
         </is>
       </c>
       <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Clean Water And Sanitation</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H23">
+        <v>54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Climate Action</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2192,7 +2258,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[2,3)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2209,60 +2280,58 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>13_g</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SDG6</t>
+          <t>SDG13</t>
         </is>
       </c>
       <c r="G24">
-        <v>136</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Clean Water And Sanitation</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H24">
+        <v>279</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Climate Action</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2272,7 +2341,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2289,60 +2363,58 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>14_g</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SDG6</t>
+          <t>SDG14</t>
         </is>
       </c>
       <c r="G25">
-        <v>19</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Clean Water And Sanitation</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life Below Water</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2352,7 +2424,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -2369,60 +2446,58 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>15_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SDG6</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G26">
-        <v>11</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Clean Water And Sanitation</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H26">
+        <v>33</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2432,7 +2507,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2529,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>15_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2464,45 +2544,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SDG7</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Affordable And Clean Energy</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H27">
+        <v>16</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2512,7 +2590,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -2529,60 +2612,58 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.a</t>
+          <t>15_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SDG7</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G28">
-        <v>170</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Affordable And Clean Energy</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2592,7 +2673,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -2609,60 +2695,58 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>15_5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SDG7</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G29">
-        <v>11</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Affordable And Clean Energy</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H29">
+        <v>178</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2672,7 +2756,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2689,60 +2778,58 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>15_7</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SDG7</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G30">
-        <v>39</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Affordable And Clean Energy</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2752,7 +2839,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -2769,60 +2861,58 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>15_g</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG15</t>
         </is>
       </c>
       <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H31">
+        <v>449</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Life On Land</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2832,7 +2922,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -2849,12 +2944,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>16_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2864,45 +2959,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG16</t>
         </is>
       </c>
       <c r="G32">
-        <v>116</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H32">
+        <v>2</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Peace, Justice And Strong Institutions</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2912,7 +3005,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>[2,3)</t>
         </is>
       </c>
     </row>
@@ -2929,60 +3027,58 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>16_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG16</t>
         </is>
       </c>
       <c r="G33">
-        <v>21</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H33">
+        <v>28</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Peace, Justice And Strong Institutions</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2992,7 +3088,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -3009,60 +3110,58 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>16_6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG16</t>
         </is>
       </c>
       <c r="G34">
-        <v>5</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H34">
+        <v>17</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Peace, Justice And Strong Institutions</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3072,7 +3171,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>[5,7)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -3089,60 +3193,58 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>16_6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG16</t>
         </is>
       </c>
       <c r="G35">
+        <v>2018</v>
+      </c>
+      <c r="H35">
         <v>2</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Peace, Justice And Strong Institutions</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3151,6 +3253,11 @@
         </is>
       </c>
       <c r="P35" t="inlineStr">
+        <is>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>[2,3)</t>
         </is>
@@ -3169,60 +3276,58 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>16_g</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG16</t>
         </is>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H36">
+        <v>26</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Peace, Justice And Strong Institutions</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3232,7 +3337,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -3249,60 +3359,58 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>17_16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SDG8</t>
+          <t>SDG17</t>
         </is>
       </c>
       <c r="G37">
-        <v>17</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Decent Work And Economic Growth</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Partnersip for Goals</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3312,7 +3420,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -3329,60 +3442,58 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>17_5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG17</t>
         </is>
       </c>
       <c r="G38">
-        <v>71</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H38">
+        <v>8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Partnersip for Goals</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3392,7 +3503,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>[7,11)</t>
         </is>
       </c>
     </row>
@@ -3409,60 +3525,58 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.b</t>
+          <t>17_g</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG17</t>
         </is>
       </c>
       <c r="G39">
-        <v>6</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H39">
+        <v>338</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Partnersip for Goals</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3472,7 +3586,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>[5,7)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -3489,60 +3608,58 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>2_1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG2</t>
         </is>
       </c>
       <c r="G40">
-        <v>49</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3552,7 +3669,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3691,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>2_2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3584,45 +3706,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG2</t>
         </is>
       </c>
       <c r="G41">
+        <v>2018</v>
+      </c>
+      <c r="H41">
         <v>1</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3631,6 +3751,11 @@
         </is>
       </c>
       <c r="P41" t="inlineStr">
+        <is>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>[1,2)</t>
         </is>
@@ -3649,12 +3774,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>2_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3664,45 +3789,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG2</t>
         </is>
       </c>
       <c r="G42">
-        <v>4</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H42">
+        <v>1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3712,7 +3835,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -3729,60 +3857,58 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>2_4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SDG9</t>
+          <t>SDG2</t>
         </is>
       </c>
       <c r="G43">
-        <v>46</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Industry, Innovation And Infrastructure</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H43">
+        <v>7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3792,7 +3918,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>[7,11)</t>
         </is>
       </c>
     </row>
@@ -3809,60 +3940,58 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>3_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SDG10</t>
+          <t>SDG3</t>
         </is>
       </c>
       <c r="G44">
+        <v>2018</v>
+      </c>
+      <c r="H44">
         <v>1</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Good Health And Well-Being</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3871,6 +4000,11 @@
         </is>
       </c>
       <c r="P44" t="inlineStr">
+        <is>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>[1,2)</t>
         </is>
@@ -3889,60 +4023,58 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10.b</t>
+          <t>3_2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SDG10</t>
+          <t>SDG3</t>
         </is>
       </c>
       <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Good Health And Well-Being</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3952,7 +4084,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>[2,3)</t>
         </is>
       </c>
     </row>
@@ -3969,60 +4106,58 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>3_6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SDG10</t>
+          <t>SDG3</t>
         </is>
       </c>
       <c r="G46">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H46">
+        <v>131</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Good Health And Well-Being</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4032,7 +4167,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -4049,60 +4189,58 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>3_a</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SDG10</t>
+          <t>SDG3</t>
         </is>
       </c>
       <c r="G47">
-        <v>2</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Good Health And Well-Being</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4112,7 +4250,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>[2,3)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -4129,60 +4272,58 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>3_g</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SDG10</t>
+          <t>SDG3</t>
         </is>
       </c>
       <c r="G48">
-        <v>7</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H48">
+        <v>400</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Good Health And Well-Being</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4192,7 +4333,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -4209,60 +4355,58 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>4_3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G49">
-        <v>3</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H49">
+        <v>2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4272,7 +4416,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>[2,3)</t>
         </is>
       </c>
     </row>
@@ -4289,60 +4438,58 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>11.b</t>
+          <t>4_4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G50">
-        <v>3</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H50">
+        <v>11</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4352,7 +4499,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -4369,60 +4521,58 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>11.b</t>
+          <t>4_5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G51">
+        <v>2018</v>
+      </c>
+      <c r="H51">
         <v>3</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4432,7 +4582,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>[3,4)</t>
         </is>
       </c>
     </row>
@@ -4449,60 +4604,58 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>4_a</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G52">
-        <v>3</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H52">
+        <v>11</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4512,7 +4665,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -4529,60 +4687,58 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>4_b</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G53">
-        <v>844</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4592,7 +4748,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -4609,60 +4770,58 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>4_g</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG4</t>
         </is>
       </c>
       <c r="G54">
-        <v>125</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H54">
+        <v>137</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4672,7 +4831,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -4689,12 +4853,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>5_5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4704,45 +4868,43 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG5</t>
         </is>
       </c>
       <c r="G55">
-        <v>16</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H55">
+        <v>13</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4752,7 +4914,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -4769,60 +4936,58 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>5_a</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SDG11</t>
+          <t>SDG5</t>
         </is>
       </c>
       <c r="G56">
-        <v>4</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sustainable Cities And Communities</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4832,7 +4997,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>[3,5)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -4849,60 +5019,58 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>5_b</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SDG12</t>
+          <t>SDG5</t>
         </is>
       </c>
       <c r="G57">
-        <v>205</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Responsible Consumption And Production</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H57">
+        <v>16</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4912,7 +5080,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -4929,60 +5102,58 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>5_g</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SDG12</t>
+          <t>SDG5</t>
         </is>
       </c>
       <c r="G58">
-        <v>38</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Responsible Consumption And Production</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H58">
+        <v>44</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4992,7 +5163,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -5009,60 +5185,58 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>6_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SDG12</t>
+          <t>SDG6</t>
         </is>
       </c>
       <c r="G59">
-        <v>88</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Responsible Consumption And Production</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Clean Water And Sanitation</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5072,7 +5246,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>[2,3)</t>
         </is>
       </c>
     </row>
@@ -5089,60 +5268,58 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>6_4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SDG12</t>
+          <t>SDG6</t>
         </is>
       </c>
       <c r="G60">
-        <v>37</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Responsible Consumption And Production</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H60">
+        <v>11</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Clean Water And Sanitation</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5152,7 +5329,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -5169,60 +5351,58 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6_b</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SDG12</t>
+          <t>SDG6</t>
         </is>
       </c>
       <c r="G61">
-        <v>56</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Responsible Consumption And Production</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H61">
+        <v>19</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Clean Water And Sanitation</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5232,7 +5412,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -5249,60 +5434,58 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>6_g</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SDG13</t>
+          <t>SDG6</t>
         </is>
       </c>
       <c r="G62">
-        <v>484</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Climate Action</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H62">
+        <v>136</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Clean Water And Sanitation</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5312,7 +5495,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -5329,60 +5517,58 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>13.a</t>
+          <t>7_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SDG13</t>
+          <t>SDG7</t>
         </is>
       </c>
       <c r="G63">
-        <v>279</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Climate Action</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H63">
+        <v>11</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Affordable And Clean Energy</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5392,7 +5578,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -5409,60 +5600,58 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>7_2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SDG13</t>
+          <t>SDG7</t>
         </is>
       </c>
       <c r="G64">
-        <v>54</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Climate Action</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Affordable And Clean Energy</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5472,7 +5661,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -5489,60 +5683,58 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>7_3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SDG14</t>
+          <t>SDG7</t>
         </is>
       </c>
       <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Life Below Water</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H65">
+        <v>39</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Affordable And Clean Energy</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5552,7 +5744,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -5569,60 +5766,58 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>7_g</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG7</t>
         </is>
       </c>
       <c r="G66">
-        <v>33</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H66">
+        <v>170</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Affordable And Clean Energy</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5632,7 +5827,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -5649,60 +5849,58 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>8_4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G67">
-        <v>16</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5712,7 +5910,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -5729,60 +5932,58 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>8_5</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G68">
-        <v>449</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H68">
+        <v>17</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5792,7 +5993,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -5809,60 +6015,58 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>8_5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H69">
+        <v>5</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5872,7 +6076,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -5889,60 +6098,58 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>8_6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G70">
-        <v>6</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H70">
+        <v>21</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5952,7 +6159,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>[5,7)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>[18,37)</t>
         </is>
       </c>
     </row>
@@ -5969,60 +6181,58 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>8_7</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SDG15</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G71">
-        <v>178</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Life On Land</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6032,7 +6242,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -6049,60 +6264,58 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>8_7</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SDG16</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G72">
+        <v>2018</v>
+      </c>
+      <c r="H72">
         <v>2</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Peace, Justice And Strong Institutions</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6111,6 +6324,11 @@
         </is>
       </c>
       <c r="P72" t="inlineStr">
+        <is>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>[2,3)</t>
         </is>
@@ -6129,60 +6347,58 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>8_g</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SDG16</t>
+          <t>SDG8</t>
         </is>
       </c>
       <c r="G73">
-        <v>26</v>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Peace, Justice And Strong Institutions</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H73">
+        <v>116</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Decent Work And Economic Growth</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6192,7 +6408,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -6209,60 +6430,58 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>9_1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SDG16</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G74">
-        <v>17</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Peace, Justice And Strong Institutions</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H74">
+        <v>71</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6272,7 +6491,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>[12,20)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -6289,60 +6513,58 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>9_2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SDG16</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Peace, Justice And Strong Institutions</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6352,7 +6574,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>[2,3)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>[1,2)</t>
         </is>
       </c>
     </row>
@@ -6369,60 +6596,58 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>9_3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SDG16</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G76">
-        <v>28</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Peace, Justice And Strong Institutions</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6432,7 +6657,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>[20,40)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -6449,60 +6679,58 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>17.16</t>
+          <t>9_5</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SDG17</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G77">
-        <v>338</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Partnersip for Goals</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H77">
+        <v>46</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6512,7 +6740,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -6529,60 +6762,58 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>9_b</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SDG17</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G78">
-        <v>8</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Partnersip for Goals</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H78">
+        <v>6</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6592,7 +6823,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>[7,12)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -6609,60 +6845,58 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>9_g</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SDG17</t>
+          <t>SDG9</t>
         </is>
       </c>
       <c r="G79">
-        <v>1</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Partnersip for Goals</t>
-        </is>
+        <v>2018</v>
+      </c>
+      <c r="H79">
+        <v>49</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industry, Innovation And Infrastructure</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6672,7 +6906,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>[1,2)</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>
@@ -6697,47 +6936,50 @@
           <t>SDGs</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
           <t>SDG</t>
         </is>
       </c>
       <c r="G80">
+        <v>2018</v>
+      </c>
+      <c r="H80">
         <v>85</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>in general</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Energy, natural resources, and basic materials</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Gravel/sand/clay</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Gravel/sand/clay</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Industrial/construction material</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>Energy, natural resources, and basic materials</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Secondary</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6747,7 +6989,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>[40,1.38e+03]</t>
+          <t>Americas</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>[37,1.38e+03]</t>
         </is>
       </c>
     </row>

--- a/Data/data_TextMining/df_Cemex_reference.xlsx
+++ b/Data/data_TextMining/df_Cemex_reference.xlsx
@@ -485,7 +485,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -495,12 +495,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -744,12 +744,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2136,7 +2136,7 @@
         <v>2018</v>
       </c>
       <c r="H22">
-        <v>484</v>
+        <v>54</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2219,7 +2219,7 @@
         <v>2018</v>
       </c>
       <c r="H23">
-        <v>54</v>
+        <v>484</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5954,7 +5954,7 @@
         <v>2018</v>
       </c>
       <c r="H68">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>[11,18)</t>
+          <t>[4,7)</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
         <v>2018</v>
       </c>
       <c r="H69">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>[4,7)</t>
+          <t>[11,18)</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Industrial/construction material</t>
+          <t>Industrial materials</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Energy, natural resources, and basic materials</t>
+          <t>Basic materials</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
